--- a/outputs/daily/hr_rankings_2026-08-01.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-01.xlsx
@@ -4442,34 +4442,30 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -13866,34 +13862,30 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -16898,34 +16890,30 @@
       </c>
       <c r="W60" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB60" t="inlineStr"/>
       <c r="AC60" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -19134,34 +19122,30 @@
       </c>
       <c r="W68" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB68" t="inlineStr"/>
       <c r="AC68" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -21644,28 +21628,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W77" t="inlineStr"/>
-      <c r="X77" t="inlineStr"/>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="Y77" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB77" t="inlineStr"/>
       <c r="AC77" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -22750,34 +22738,30 @@
       </c>
       <c r="W81" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X81" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y81" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB81" t="inlineStr"/>
       <c r="AC81" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -33002,34 +32986,30 @@
       </c>
       <c r="W118" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X118" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y118" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 8</t>
-        </is>
-      </c>
+      <c r="AB118" t="inlineStr"/>
       <c r="AC118" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -36864,28 +36844,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W132" t="inlineStr"/>
-      <c r="X132" t="inlineStr"/>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X132" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="Y132" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB132" t="inlineStr"/>
       <c r="AC132" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -52040,28 +52024,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W187" t="inlineStr"/>
-      <c r="X187" t="inlineStr"/>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X187" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="Y187" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z187" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z187" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA187" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB187" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB187" t="inlineStr"/>
       <c r="AC187" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -79444,34 +79432,30 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>

--- a/outputs/daily/hr_rankings_2026-08-01.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-01.xlsx
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5304,28 +5304,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="Y18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6356,7 +6360,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -7196,7 +7200,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -7756,7 +7760,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -8876,7 +8880,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -9716,7 +9720,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -10556,7 +10560,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -11116,7 +11120,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -12516,7 +12520,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -12580,28 +12584,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W44" t="inlineStr"/>
-      <c r="X44" t="inlineStr"/>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="Y44" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -13072,7 +13080,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -13912,7 +13920,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -16152,7 +16160,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -18952,7 +18960,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -19023,7 +19031,7 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
@@ -19033,7 +19041,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -19041,11 +19049,7 @@
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>order MLB 8 vs RotoWire 2</t>
-        </is>
-      </c>
+      <c r="AB67" t="inlineStr"/>
       <c r="AC67" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -20076,7 +20080,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -21196,7 +21200,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -22036,7 +22040,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -22596,7 +22600,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -22872,7 +22876,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -23712,7 +23716,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -25112,7 +25116,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -25948,7 +25952,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -26508,7 +26512,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -27348,7 +27352,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -27908,7 +27912,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -28188,7 +28192,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -28748,7 +28752,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -29028,7 +29032,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -29864,7 +29868,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -30704,7 +30708,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -32384,7 +32388,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -32455,7 +32459,7 @@
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y115" t="inlineStr">
@@ -32465,7 +32469,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -32473,11 +32477,7 @@
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>order MLB 6 vs RotoWire 9</t>
-        </is>
-      </c>
+      <c r="AB115" t="inlineStr"/>
       <c r="AC115" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -34908,7 +34908,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -35188,7 +35188,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -35464,7 +35464,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -37704,7 +37704,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -39944,7 +39944,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -40224,7 +40224,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -40784,7 +40784,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -41620,7 +41620,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -44140,7 +44140,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -44416,7 +44416,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -44692,7 +44692,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -46372,7 +46372,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -46648,7 +46648,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -46719,7 +46719,7 @@
       </c>
       <c r="X166" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y166" t="inlineStr">
@@ -46729,7 +46729,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -46737,11 +46737,7 @@
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB166" t="inlineStr">
-        <is>
-          <t>order MLB 9 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB166" t="inlineStr"/>
       <c r="AC166" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -46932,7 +46928,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -47772,7 +47768,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -48052,7 +48048,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -48888,7 +48884,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -49168,7 +49164,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -50008,7 +50004,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -52014,7 +52010,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -52574,7 +52570,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -53974,7 +53970,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -54254,7 +54250,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -55374,7 +55370,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -55934,7 +55930,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -55998,28 +55994,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="Y18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
